--- a/tests/fixtures/check/IREX_Rehab_Data_Collection_CY2025.xlsx
+++ b/tests/fixtures/check/IREX_Rehab_Data_Collection_CY2025.xlsx
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
@@ -1491,6 +1491,74 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>https://example.com/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tan Wei Ling</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Therapy tips video</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TestTube</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://example.com/v</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tan Wei Ling</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Therapy tips video</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TestTube</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://example.com/v</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MED-0005</t>
         </is>
       </c>
     </row>
